--- a/ProyectoVisitas/wwwroot/Templates/ListaDeAsistencia.xlsx
+++ b/ProyectoVisitas/wwwroot/Templates/ListaDeAsistencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ProyectoVisitas\ProyectoVisitas\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16220A4E-4FCC-4365-92D0-7A4EF3199318}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA4695A-07D4-4C60-91C5-342FEC49D49D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>NO.</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>DOMICILIO Y RESPONSABLE:                                                                                                     Responsable: LIC. Blanca Pacheco                                                         Domicilio: Blvd. Miguel de Cervantes Saavedra #8701 Col. Colinas de Santa Julia</t>
-  </si>
-  <si>
-    <t>FECHA                               FOLIO</t>
   </si>
   <si>
     <t xml:space="preserve">      LISTA ASISTENCIA DE JUZGADO CÍVICO </t>
@@ -361,9 +358,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -378,6 +372,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -864,7 +861,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -879,12 +876,10 @@
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
-      <c r="D2" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1064,14 +1059,14 @@
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1084,15 +1079,15 @@
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="28"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>

--- a/ProyectoVisitas/wwwroot/Templates/ListaDeAsistencia.xlsx
+++ b/ProyectoVisitas/wwwroot/Templates/ListaDeAsistencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ProyectoVisitas\ProyectoVisitas\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA4695A-07D4-4C60-91C5-342FEC49D49D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C199ADF-8C70-4F41-A966-BE01ECC9D0B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,6 +358,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -372,9 +375,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -851,10 +851,10 @@
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="5" customWidth="1"/>
     <col min="7" max="7" width="27.7109375" style="1" customWidth="1"/>
     <col min="8" max="16384" width="11.42578125" style="1"/>
   </cols>
@@ -876,10 +876,10 @@
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1059,14 +1059,14 @@
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1079,15 +1079,15 @@
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>

--- a/ProyectoVisitas/wwwroot/Templates/ListaDeAsistencia.xlsx
+++ b/ProyectoVisitas/wwwroot/Templates/ListaDeAsistencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ProyectoVisitas\ProyectoVisitas\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C199ADF-8C70-4F41-A966-BE01ECC9D0B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8697082-9795-4593-ABFA-657319A02697}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +130,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -295,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -370,11 +378,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,13 +545,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -846,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1047,7 +1058,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -1058,65 +1069,133 @@
       <c r="F17" s="8"/>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
+    <row r="18" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="3"/>
+      <c r="I18" s="30"/>
+    </row>
+    <row r="19" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="3"/>
+      <c r="I20" s="30"/>
+    </row>
+    <row r="21" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="11"/>
-    </row>
-    <row r="19" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="20" t="s">
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="28"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18"/>
+      <c r="B27" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="21"/>
-    </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
